--- a/diseases/d058/2000-2004.xlsx
+++ b/diseases/d058/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.01062846812229064</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>4</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.0148798553712069</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>1007</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>2.140573479829336</v>
       </c>
@@ -2245,9 +2215,6 @@
       <c r="O12" t="n">
         <v>1499</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>3.186414743062735</v>
       </c>
@@ -2393,9 +2360,6 @@
       <c r="O13" t="n">
         <v>107</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.2274492178170198</v>
       </c>
@@ -2541,9 +2505,6 @@
       <c r="O14" t="n">
         <v>6</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.0126852252992738</v>
       </c>
@@ -2689,9 +2650,6 @@
       <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -2837,9 +2795,6 @@
       <c r="O16" t="n">
         <v>3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -2985,9 +2940,6 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -3133,9 +3085,6 @@
       <c r="O18" t="n">
         <v>7</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.01479942951581943</v>
       </c>
@@ -3281,9 +3230,6 @@
       <c r="O19" t="n">
         <v>7</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.01479942951581943</v>
       </c>
@@ -3429,9 +3375,6 @@
       <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -3577,9 +3520,6 @@
       <c r="O21" t="n">
         <v>5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -3725,9 +3665,6 @@
       <c r="O22" t="n">
         <v>22</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.04651249276400393</v>
       </c>
@@ -3873,9 +3810,6 @@
       <c r="O23" t="n">
         <v>962</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>2.033864456316899</v>
       </c>
@@ -4021,9 +3955,6 @@
       <c r="O24" t="n">
         <v>843</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.782274154547969</v>
       </c>
@@ -4169,9 +4100,6 @@
       <c r="O25" t="n">
         <v>57</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1205096403431011</v>
       </c>
@@ -4317,9 +4245,6 @@
       <c r="O26" t="n">
         <v>5</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -4613,9 +4538,6 @@
       <c r="O28" t="n">
         <v>3</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -4909,9 +4831,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -5205,9 +5124,6 @@
       <c r="O32" t="n">
         <v>4</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.008418542931006853</v>
       </c>
@@ -5501,9 +5417,6 @@
       <c r="O34" t="n">
         <v>7</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.01473245012926199</v>
       </c>
@@ -5797,9 +5710,6 @@
       <c r="O36" t="n">
         <v>6</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.01262781439651028</v>
       </c>
@@ -6093,9 +6003,6 @@
       <c r="O38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -6389,9 +6296,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -6685,9 +6589,6 @@
       <c r="O42" t="n">
         <v>9</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.01894172159476542</v>
       </c>
@@ -6981,9 +6882,6 @@
       <c r="O44" t="n">
         <v>642</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>1.3511761404266</v>
       </c>
@@ -7277,9 +7175,6 @@
       <c r="O46" t="n">
         <v>642</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>1.3511761404266</v>
       </c>
@@ -7573,9 +7468,6 @@
       <c r="O48" t="n">
         <v>91</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.1915218516804059</v>
       </c>
@@ -7869,9 +7761,6 @@
       <c r="O50" t="n">
         <v>7</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.01467595219753043</v>
       </c>
@@ -8165,9 +8054,6 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -8461,9 +8347,6 @@
       <c r="O54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -8757,9 +8640,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -9053,9 +8933,6 @@
       <c r="O58" t="n">
         <v>6</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -9349,9 +9226,6 @@
       <c r="O60" t="n">
         <v>6</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -9645,9 +9519,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -9941,9 +9812,6 @@
       <c r="O64" t="n">
         <v>6</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -10237,9 +10105,6 @@
       <c r="O66" t="n">
         <v>14</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.02935190439506087</v>
       </c>
@@ -10533,9 +10398,6 @@
       <c r="O68" t="n">
         <v>1829</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>3.834616652754737</v>
       </c>
@@ -10829,9 +10691,6 @@
       <c r="O70" t="n">
         <v>2667</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>5.591537787259095</v>
       </c>
@@ -11124,9 +10983,6 @@
       </c>
       <c r="O72" t="n">
         <v>158</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0.3312572067442583</v>
